--- a/src/classifications/cde_delete.xlsx
+++ b/src/classifications/cde_delete.xlsx
@@ -132,10 +132,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/src/classifications/cde_delete.xlsx
+++ b/src/classifications/cde_delete.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wavicledata-my.sharepoint.com/personal/rajesh_puchakayala_wavicledata_com/Documents/Desktop/project/perview/src/classifications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_71F24F94407219B5A74575F6183D3E4314525CC4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C47B2A7A-D25E-4F3E-B568-441E396A51FA}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="11_71F24F94407219B5A74575F6183D3E4314525CC4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2531C874-1249-4F6C-B53D-F67C86CE6F1B}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="14927" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="6">
   <si>
     <t>column_name</t>
   </si>
@@ -38,12 +38,18 @@
   <si>
     <t xml:space="preserve"> </t>
   </si>
+  <si>
+    <t>credit_card_number</t>
+  </si>
+  <si>
+    <t>MICROSOFT.GOVERNMENT.AUSTRIA.IDENTITY.CARD</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -65,6 +71,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF242424"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="20"/>
       <color rgb="FF242424"/>
       <name val="Segoe UI"/>
       <family val="2"/>
@@ -110,13 +122,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -547,7 +560,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -562,6 +575,14 @@
         <v>1</v>
       </c>
     </row>
+    <row r="2" spans="1:2" ht="29.95" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/src/classifications/cde_delete.xlsx
+++ b/src/classifications/cde_delete.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wavicledata-my.sharepoint.com/personal/rajesh_puchakayala_wavicledata_com/Documents/Desktop/project/perview/src/classifications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="11_71F24F94407219B5A74575F6183D3E4314525CC4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2531C874-1249-4F6C-B53D-F67C86CE6F1B}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="11_71F24F94407219B5A74575F6183D3E4314525CC4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{516893F7-269A-409E-8308-75497184970D}"/>
   <bookViews>
-    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="14927" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="14927" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SQL Server" sheetId="1" r:id="rId1"/>
@@ -145,6 +145,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -538,6 +542,36 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="29.95" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -556,34 +590,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="35" customWidth="1"/>
-    <col min="2" max="2" width="60" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="29.95" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>